--- a/tests/fixtures/step3_column_collision_test.xlsx
+++ b/tests/fixtures/step3_column_collision_test.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Wide_to_long衝突" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="クロス集計衝突" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="括弧注釈衝突" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="階層圧縮衝突" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,4 +518,156 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>拠点</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>拠点種別</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>売上</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東京（本社）</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>直営</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>大阪（支社）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>代理店</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>980</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>組織階層</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>地域</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>売上</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東日本</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>首都圏</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  東京支社</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>首都圏</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>西日本</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>関西圏</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  大阪支社</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>関西圏</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>